--- a/data/trans_bre/P38B-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P38B-Edad-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,9; 18,35</t>
+          <t>4,6; 18,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,12; 16,02</t>
+          <t>2,34; 15,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 22,22</t>
+          <t>-0,62; 21,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,75; 40,51</t>
+          <t>9,06; 41,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,77; 31,24</t>
+          <t>3,89; 29,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,01; 53,98</t>
+          <t>-0,79; 53,41</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,04; 13,23</t>
+          <t>4,15; 13,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,43; 17,55</t>
+          <t>7,19; 17,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-25,48; 13,18</t>
+          <t>-22,54; 13,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,25; 17,98</t>
+          <t>5,31; 17,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,25; 26,21</t>
+          <t>10,0; 26,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-38,93; 20,44</t>
+          <t>-35,57; 20,97</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 8,44</t>
+          <t>1,5; 8,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 7,98</t>
+          <t>-0,41; 7,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,51; 11,66</t>
+          <t>2,8; 11,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 10,08</t>
+          <t>1,71; 10,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 10,08</t>
+          <t>-0,65; 9,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,21; 15,84</t>
+          <t>3,53; 15,99</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 3,82</t>
+          <t>-3,49; 3,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 6,06</t>
+          <t>-0,71; 6,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,49; 65,74</t>
+          <t>3,54; 62,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 4,33</t>
+          <t>-3,78; 4,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 6,99</t>
+          <t>-0,76; 7,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,99; 249,48</t>
+          <t>4,06; 210,31</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 5,11</t>
+          <t>-1,26; 5,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 4,67</t>
+          <t>-2,14; 4,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 5,08</t>
+          <t>-0,44; 4,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 5,68</t>
+          <t>-1,3; 5,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 5,19</t>
+          <t>-2,25; 5,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 5,59</t>
+          <t>-0,47; 5,32</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 2,48</t>
+          <t>-4,44; 2,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 2,78</t>
+          <t>-1,75; 2,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,65; 5,17</t>
+          <t>0,62; 5,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 2,63</t>
+          <t>-4,53; 2,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 2,88</t>
+          <t>-1,76; 2,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,65; 5,49</t>
+          <t>0,63; 5,5</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 8,13</t>
+          <t>0,22; 7,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 2,24</t>
+          <t>-2,39; 2,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,94; -0,46</t>
+          <t>-4,24; -0,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 9,12</t>
+          <t>0,25; 8,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 2,3</t>
+          <t>-2,42; 2,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,01; -0,47</t>
+          <t>-4,28; -0,85</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,96; 7,34</t>
+          <t>3,8; 7,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,81; 7,27</t>
+          <t>3,76; 7,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,37; 31,2</t>
+          <t>4,51; 27,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,75; 9,03</t>
+          <t>4,6; 9,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,59; 9,01</t>
+          <t>4,55; 9,04</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,38; 54,37</t>
+          <t>5,51; 46,01</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P38B-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P38B-Edad-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10,64</t>
+          <t>13,41</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>29,7%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,6; 18,44</t>
+          <t>5,53; 18,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,34; 15,12</t>
+          <t>2,04; 15,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 21,92</t>
+          <t>3,75; 24,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,06; 41,46</t>
+          <t>10,61; 42,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,89; 29,2</t>
+          <t>3,61; 30,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 53,41</t>
+          <t>7,33; 62,67</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>10,99</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>17,04%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,15; 13,13</t>
+          <t>4,61; 12,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,19; 17,22</t>
+          <t>7,22; 17,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-22,54; 13,33</t>
+          <t>3,64; 17,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,31; 17,93</t>
+          <t>6,01; 17,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,0; 26,09</t>
+          <t>10,07; 26,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,57; 20,97</t>
+          <t>5,23; 30,57</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,27</t>
+          <t>9,09</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 8,58</t>
+          <t>0,92; 8,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 7,73</t>
+          <t>-0,53; 7,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,8; 11,74</t>
+          <t>4,51; 14,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 10,32</t>
+          <t>1,01; 10,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 9,59</t>
+          <t>-0,69; 9,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,53; 15,99</t>
+          <t>5,75; 19,52</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28,78</t>
+          <t>3,37</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 3,84</t>
+          <t>-3,58; 3,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 6,28</t>
+          <t>-0,75; 6,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,54; 62,67</t>
+          <t>0,26; 6,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 4,35</t>
+          <t>-3,84; 4,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 7,31</t>
+          <t>-0,82; 7,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,06; 210,31</t>
+          <t>0,3; 7,63</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,27</t>
+          <t>3,41</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 5,36</t>
+          <t>-1,33; 5,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 4,84</t>
+          <t>-2,06; 5,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 4,82</t>
+          <t>0,65; 5,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 5,86</t>
+          <t>-1,38; 5,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 5,41</t>
+          <t>-2,18; 5,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 5,32</t>
+          <t>0,68; 6,48</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2,62</t>
+          <t>1,97</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 2,31</t>
+          <t>-4,36; 2,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 2,62</t>
+          <t>-1,86; 2,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,62; 5,14</t>
+          <t>-0,04; 4,2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 2,46</t>
+          <t>-4,45; 2,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 2,74</t>
+          <t>-1,87; 2,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,5</t>
+          <t>-0,02; 4,5</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-2,37</t>
+          <t>-2,46</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,4%</t>
+          <t>-2,49%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,22; 7,91</t>
+          <t>0,34; 8,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 2,3</t>
+          <t>-2,19; 2,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,24; -0,83</t>
+          <t>-4,33; -0,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,25; 8,81</t>
+          <t>0,35; 9,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 2,37</t>
+          <t>-2,24; 2,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,28; -0,85</t>
+          <t>-4,35; -0,71</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11,37</t>
+          <t>6,75</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,8; 7,3</t>
+          <t>3,96; 7,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,76; 7,3</t>
+          <t>3,63; 7,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,51; 27,68</t>
+          <t>4,71; 8,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,6; 9,02</t>
+          <t>4,79; 9,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,55; 9,04</t>
+          <t>4,4; 9,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,51; 46,01</t>
+          <t>5,77; 11,06</t>
         </is>
       </c>
     </row>
